--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137171819</v>
       </c>
       <c r="B3" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137170286</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137170362</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137170470</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137170671</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137170889</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137171217</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137171261</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137171314</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137171598</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137171724</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137171009</v>
       </c>
       <c r="B14" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137171528</v>
       </c>
       <c r="B15" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137171794</v>
       </c>
       <c r="B16" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137171819</v>
       </c>
       <c r="B3" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137170286</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137170362</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137170470</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137170671</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137170889</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137171217</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137171261</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137171314</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137171598</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137171724</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137171009</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137171528</v>
       </c>
       <c r="B15" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137171794</v>
       </c>
       <c r="B16" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137171388</v>
       </c>
       <c r="B17" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137171163</v>
       </c>
       <c r="B18" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137170305</v>
       </c>
       <c r="B19" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137171819</v>
       </c>
       <c r="B3" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137170286</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137170362</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137170470</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137170671</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137170889</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137171217</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137171261</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137171314</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137171598</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137171724</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137171009</v>
       </c>
       <c r="B14" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137171528</v>
       </c>
       <c r="B15" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137171794</v>
       </c>
       <c r="B16" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137171388</v>
       </c>
       <c r="B17" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137171163</v>
       </c>
       <c r="B18" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>137170305</v>
       </c>
       <c r="B19" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -2501,16 +2501,8 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hästknopparna, Dlr</t>
@@ -2628,11 +2620,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hästknopparna, Dlr</t>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137171819</v>
       </c>
       <c r="B3" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137170286</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137170362</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137170470</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137170671</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137170889</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137171217</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137171261</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137171314</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137171598</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137171724</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137171009</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137171528</v>
       </c>
       <c r="B15" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137171794</v>
       </c>
       <c r="B16" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137171388</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137171163</v>
       </c>
       <c r="B18" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>137170305</v>
       </c>
       <c r="B19" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137171819</v>
       </c>
       <c r="B3" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137170286</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137170362</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137170470</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137170671</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137170889</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137171217</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137171261</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137171314</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137171598</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137171724</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137171009</v>
       </c>
       <c r="B14" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137171528</v>
       </c>
       <c r="B15" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137171794</v>
       </c>
       <c r="B16" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137171388</v>
       </c>
       <c r="B17" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137171163</v>
       </c>
       <c r="B18" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>137170305</v>
       </c>
       <c r="B19" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137171819</v>
       </c>
       <c r="B3" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137170286</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137170362</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137170470</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137170671</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137170889</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137171217</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137171261</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137171314</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137171598</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137171724</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137171009</v>
       </c>
       <c r="B14" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137171528</v>
       </c>
       <c r="B15" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137171794</v>
       </c>
       <c r="B16" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137171388</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>137170305</v>
       </c>
       <c r="B19" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137171819</v>
       </c>
       <c r="B3" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137170286</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137170362</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137170470</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137170671</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137170889</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137171217</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137171261</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137171314</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137171598</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137171724</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137171009</v>
       </c>
       <c r="B14" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137171528</v>
       </c>
       <c r="B15" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137171794</v>
       </c>
       <c r="B16" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137171819</v>
       </c>
       <c r="B3" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137170286</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137170362</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137170470</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137170671</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137170889</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137171217</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137171261</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137171314</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137171598</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137171724</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137171009</v>
       </c>
       <c r="B14" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137171528</v>
       </c>
       <c r="B15" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137171794</v>
       </c>
       <c r="B16" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137171819</v>
       </c>
       <c r="B3" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137170286</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137170362</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137170470</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137170671</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137170889</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137171217</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137171261</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137171314</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137171598</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137171724</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137171009</v>
       </c>
       <c r="B14" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137171528</v>
       </c>
       <c r="B15" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137171794</v>
       </c>
       <c r="B16" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37575-2026 artfynd.xlsx
+++ b/artfynd/A 37575-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137170929</v>
       </c>
       <c r="B2" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137171819</v>
       </c>
       <c r="B3" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137170286</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137170362</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137170470</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137170671</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137170889</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137171217</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137171261</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137171314</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137171598</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137171724</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137171009</v>
       </c>
       <c r="B14" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137171528</v>
       </c>
       <c r="B15" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137171794</v>
       </c>
       <c r="B16" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137171388</v>
       </c>
       <c r="B17" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137171163</v>
       </c>
       <c r="B18" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>137170305</v>
       </c>
       <c r="B19" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
